--- a/data/analysis/experience_profiles.xlsx
+++ b/data/analysis/experience_profiles.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Candidate 32_QAISAR_HUSSAIN_ALVI has 21.2 years of experience with upward career progression. They have a total of 4 timeline events with no overlaps, but 1 gap detected. The candidate's skills do not have strong evidence and have low alignment with the job description.</t>
+          <t>Candidate Qaisar Hussain Alvi possesses 21.2 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 4 recorded activity event(s), with 0 overlap(s) and 1 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Strong Profile.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Candidate 33_QAMAR_ABBAS has 8 years of stable career progression with 3 notable timeline events. They have strong evidence of skills in IoT. However, their job description alignment score is low at 0.0%, indicating a potential mismatch between their skills and the job requirements.</t>
+          <t>Candidate Qamar Abbas possesses 8.0 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 3 recorded activity event(s), with 0 overlap(s) and 0 gap(s) identified. Proven technical competencies include IoT, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Strong Profile.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Candidate 04_MUHAMMAD_FARRUKH has 11.2 years of experience with upward career progression. They have demonstrated expertise in Deep Learning and Machine Learning, but their job description alignment is low at 18.2%. The candidate has some gaps and overlaps in their timeline, which may require further clarification.</t>
+          <t>Candidate Muhammad Farrukh Qureshi possesses 11.2 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 7 recorded activity event(s), with 4 overlap(s) and 1 gap(s) identified. Proven technical competencies include Deep Learning, Machine Learning, achieving a 18.2% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Candidate 05_MUHAMMAD_MAJID has 4.9 years of experience with a stable career progression. However, there are concerns regarding unjustified gaps and low job description alignment, which may impact their suitability for the role.</t>
+          <t>Candidate MUHAMMAD MAJID possesses 4.9 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 7 recorded activity event(s), with 1 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Candidate 08_TAYYABA_GULL has 7.9 years of experience with upward career progression. However, they have 4 unjustified gaps and 3 overlaps in their timeline, indicating some inconsistencies. Their JD alignment score is low at 0.0%, suggesting a need for further skill development.</t>
+          <t>Candidate Tayyaba Gull possesses 7.9 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Candidate 15_M_USMAN_ABBASI has 16.7 years of experience with upward career progression. However, there are concerns with 5 overlaps, including 1 suspicious overlap, and 2 gaps, including 1 unjustified gap. The candidate's skills do not align well with the job description, with a JD alignment score of 0.0%. Further clarification is needed to understand the candidate's strengths and weaknesses.</t>
+          <t>Candidate M. Usman Abbasi possesses 16.7 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 7 recorded activity event(s), with 5 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Candidate 16_MUZZAMIL_GHAFFAR has 14.3 years of experience with upward career progression. However, there are concerns with 4 overlaps, including 1 suspicious overlap, and 3 gaps, including 2 unjustified gaps. The candidate's skills are not strongly aligned with the job description, with a JD alignment score of 0.0%. Further clarification is needed to confirm the candidate's skills and experience.</t>
+          <t>Candidate Muzzamil Ghaffar possesses 14.3 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 4 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Candidate 20_SYED_FASIH_ALI has 2.4 years of experience with upward career progression. However, there are concerns with 2 suspicious overlaps and 2 unjustified gaps in their timeline. Additionally, their skills do not align with the job description, with only 1 verified skill in IoT.</t>
+          <t>Candidate Syed Fasih Ali possesses 2.4 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 7 recorded activity event(s), with 2 overlap(s) and 3 gap(s) identified. Proven technical competencies include IoT, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Candidate 26_AAMINA_AKBAR has 12 years of stable career progression with 7 notable timeline events. However, there are concerns with 3 overlaps, including 1 suspicious instance, and 2 gaps, with 1 unjustified gap. The candidate's skills do not have strong evidence, and their job description alignment is low at 0.0%. Further clarification is needed to fully assess their qualifications.</t>
+          <t>Candidate Aamina Akbar possesses 12.0 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 7 recorded activity event(s), with 3 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Candidate 35_MATIULLAH_AHSAN has 2.2 years of professional experience, with a career progression of Early Career. They have a total of 7 timeline events, with 2 overlaps and 3 gaps, including 2 unjustified gaps. The candidate's skills have low alignment with the job description, with a JD alignment score of 4.5%.</t>
+          <t>Candidate Matiullah Ahsan possesses 2.2 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 7 recorded activity event(s), with 2 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Candidate 36_SAMANA_BATOOL has 8.4 years of experience with upward career progression. However, there are gaps in their timeline and low alignment with the job description. They have a total of 4 timeline events with 1 overlap and 2 gaps, including 1 unjustified gap.</t>
+          <t>Candidate Samana Batool possesses 8.4 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 4 recorded activity event(s), with 1 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Candidate 41_MUHAMMAD_AQEEL has 4.2 years of stable career progression with 6 notable timeline events. They possess strong evidence of skills in Deep Learning, Image Processing, and IoT. However, their job description alignment is low at 18.2%, indicating potential gaps in their skill set.</t>
+          <t>Candidate Muhammad Aqeel possesses 4.2 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 6 recorded activity event(s), with 1 overlap(s) and 1 gap(s) identified. Proven technical competencies include Deep Learning, Image Processing, IoT, achieving a 18.2% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Candidate 01_MUHAMMAD_SALMAN has 19 years of experience with upward career progression. However, the presence of suspicious overlaps and unjustified gaps in their timeline raises concerns. Additionally, the low JD alignment score indicates limited skill relevance to the job description.</t>
+          <t>Candidate MUHAMMAD SALMAN possesses 19.0 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 1 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Candidate 02_MUHAMMAD_SHAHWAZ has 0.7 years of experience with a stable career progression. However, they have 4 unjustified gaps and 2 suspicious overlaps in their timeline, indicating potential inconsistencies. Additionally, their skills do not align well with the job description, with a JD alignment score of 0.0%.</t>
+          <t>Candidate MUHAMMAD SHAHWAZ possesses 0.7 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 8 recorded activity event(s), with 2 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Candidate 03_NASIR_ALI_SHAH has 2.9 years of experience with a stable career progression. However, the presence of 4 unjustified gaps and 7 overlaps, including 3 suspicious ones, raises concerns about the accuracy of their timeline. Despite having strong evidence for IoT and Machine Learning skills, the low JD alignment score of 9.1% indicates a need for further clarification.</t>
+          <t>Candidate Nasir Ali Shah possesses 2.9 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 10 recorded activity event(s), with 7 overlap(s) and 4 gap(s) identified. Proven technical competencies include IoT, Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Candidate 06_FARMAN_ALI has 11.9 years of experience with a steady career progression. However, there are concerns about overlap and unjustified gaps in their timeline, which may indicate a need for further clarification. Additionally, their skills do not strongly align with the job description, suggesting a developing profile.</t>
+          <t>Candidate Farman Ali possesses 11.9 years of total professional experience demonstrating a steady career path trajectory. Their unified timeline contains 9 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Candidate 07_FIZA_MURTAZA has 13.8 years of experience with upward career progression. However, the candidate has a high number of overlaps and gaps in their timeline, which may indicate inconsistencies. Additionally, the JD alignment score is low at 9.1%, suggesting a need for further skill development.</t>
+          <t>Candidate Fiza Murtaza possesses 13.8 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 14 recorded activity event(s), with 12 overlap(s) and 1 gap(s) identified. Proven technical competencies include Computer Vision, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Candidate 09_MUHAMMAD_ABUBAKAR has 9.1 years of experience with upward career progression. However, there are concerns with 3 overlaps, 4 gaps, and low JD alignment score of 22.7%. The candidate has strong evidence of skills in Deep Learning and Machine Learning.</t>
+          <t>Candidate Muhammad Abubakar possesses 9.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include Deep Learning, Machine Learning, achieving a 22.7% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Candidate 10_MUHAMMAD_EHATISHAM has 9.9 years of experience with a stable career progression. However, the presence of suspicious overlaps and unjustified gaps in their timeline raises concerns. Additionally, the candidate lacks strong evidence of relevant skills and has low job description alignment.</t>
+          <t>Candidate Muhammad Ehatisham possesses 9.9 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 11 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Candidate 11_WAQAS_AMIN has 14 years of experience with upward career progression. However, there are concerns regarding unjustified gaps and suspicious overlaps in their timeline. Additionally, their skill evidence is limited, with only one verified skill in Cybersecurity, and a low JD alignment score of 0.0%. Further clarification is needed to fully assess their qualifications.</t>
+          <t>Candidate Waqas Amin possesses 14.0 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 3 gap(s) identified. Proven technical competencies include Cybersecurity, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Candidate 12_SYED_TAMOORULHASSAN has 15.2 years of experience with a stable career progression. However, there are concerns with 4 suspicious overlaps and 2 unjustified gaps in their timeline. Additionally, their JD alignment score is low at 9.1%, indicating limited skill alignment with the job description.</t>
+          <t>Candidate SYED TAMOORULHASSAN possesses 15.2 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 10 recorded activity event(s), with 4 overlap(s) and 2 gap(s) identified. Proven technical competencies include Wireless Networks, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Candidate 13_MANZOOR_ELLAHI has 17.8 years of experience with upward career progression. However, there are concerns regarding overlaps and unjustified gaps in their timeline. They possess strong evidence of skills in IoT and Machine Learning, but their job description alignment is low at 9.1%. Further clarification is needed to fully assess their profile.</t>
+          <t>Candidate Manzoor Ellahi possesses 17.8 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include IoT, Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Candidate 14_SAROSH_TAHIR has 17.3 years of experience with a stable career progression. However, there are concerns about suspicious overlaps and unjustified gaps in their timeline. Additionally, their skills do not strongly align with the job description, indicating a need for further development.</t>
+          <t>Candidate Sarosh Tahir possesses 17.3 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 12 recorded activity event(s), with 6 overlap(s) and 1 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Candidate 17_SUHAIL_ASGHAR has 0.8 years of experience, with a career progression of Early Career. They have 6 timeline events, with 2 overlaps and 2 gaps, indicating potential inconsistencies in their experience. The candidate's skills do not align with the job description, with a JD alignment score of 0.0%.</t>
+          <t>Candidate Suhail Asghar Qureshi possesses 0.8 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 6 recorded activity event(s), with 2 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Amjad has 8.9 years of experience with upward career progression. However, there are concerns regarding 11 suspicious overlaps and 4 unjustified gaps in their timeline. Additionally, they lack strong evidence of skills and have low job description alignment.</t>
+          <t>Candidate Muhammad Amjad possesses 8.9 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 11 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Candidate 19_ASIM_MASOOD has 12.1 years of experience with upward career progression. However, they have 3 suspicious overlaps and 3 unjustified gaps in their timeline. Additionally, their JD alignment score is low at 9.1%, indicating limited skill alignment with the job description.</t>
+          <t>Candidate Asim Masood possesses 12.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Candidate 21_SAMAN_FATIMA has 5.1 years of experience with upward career progression. However, their experience timeline is marred by 3 suspicious overlaps and 3 unjustified gaps. Additionally, they lack strong evidence of key skills and have low job description alignment, indicating areas for development.</t>
+          <t>Candidate Saman Fatima possesses 5.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Candidate 22_ZEESHAN has 1.5 years of experience, with a career progression of Early Career. Their experience timeline is marked by 3 unjustified gaps and 2 suspicious overlaps. The candidate lacks strong evidence of relevant skills, with a low JD alignment score of 0.0%.</t>
+          <t>Candidate Zeeshan possesses 1.5 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 6 recorded activity event(s), with 2 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Candidate 23_WAQAS_TARIQ_TOOR has 17.4 years of experience with upward career progression. However, there are concerns regarding unjustified gaps and suspicious overlaps in their timeline. They possess strong evidence of skills in Artificial Intelligence, Deep Learning, and IoT, but their job description alignment is low at 27.3%. Further clarification is needed to fully assess their profile.</t>
+          <t>Candidate Waqas Tariq Toor possesses 17.4 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 5 overlap(s) and 3 gap(s) identified. Proven technical competencies include Artificial Intelligence, Deep Learning, IoT, achieving a 27.3% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Candidate 24_AHMED_NAEEM has 6.5 years of experience with a steady career progression. However, they have 3 overlaps, 2 of which are suspicious, and a low JD alignment score of 4.5%. Further clarification is needed to fully assess their skills and experience.</t>
+          <t>Candidate Ahmed Naeem possesses 6.5 years of total professional experience demonstrating a steady career path trajectory. Their unified timeline contains 6 recorded activity event(s), with 3 overlap(s) and 0 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Candidate 25_MUHAMMAD_ADEEL_ALTAF has 4.7 years of experience with upward career progression. However, their experience timeline shows 4 gaps and 4 overlaps, with 2 suspicious overlaps and 2 unjustified gaps. The candidate lacks strong evidence of skills and has low job description alignment at 4.5%. Further clarification is needed to fully assess their profile.</t>
+          <t>Candidate MUHAMMAD ADEEL ALTAF possesses 4.7 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 8 recorded activity event(s), with 4 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Candidate 27_SHAHEER has 22 years of experience with upward career progression. However, the presence of 8 suspicious overlaps and 2 unjustified gaps in their timeline raises concerns. Additionally, the candidate lacks strong evidence of relevant skills and has low job description alignment, indicating areas for development.</t>
+          <t>Candidate Shaheer possesses 22.0 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 8 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Candidate 29_MUHAMMAD_SARMAD_TARIQ has 1.6 years of experience with early career progression. Their experience timeline contains 6 events with 2 overlaps and 2 gaps, including 1 unjustified gap. The candidate lacks strong evidence of relevant skills and has low job description alignment.</t>
+          <t>Candidate Muhammad Sarmad Tariq possesses 1.6 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 6 recorded activity event(s), with 2 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Candidate 30_FAHD_SIKANDAR_KHAN has 9.7 years of experience with a stable career progression. However, their experience timeline shows 5 overlaps, 3 gaps, and no strong evidence skills. The JD alignment score is low at 0.0%, indicating a need for further clarification on their skill alignment.</t>
+          <t>Candidate Fahd Sikandar Khan possesses 9.7 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 12 recorded activity event(s), with 5 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Candidate 34_SHAHZAD has 9.3 years of experience with upward career progression. However, there are concerns with 4 overlaps, 1 unjustified gap, and low job description alignment score of 4.5%. The candidate has strong evidence of skills in IoT.</t>
+          <t>Candidate Shahzad possesses 9.3 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 4 overlap(s) and 1 gap(s) identified. Proven technical competencies include IoT, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Candidate 37_SANIA_GUL has 16 years of experience with upward career progression. However, there are concerns regarding suspicious overlaps and unjustified gaps in their timeline. Additionally, their skills do not strongly align with the job description, indicating a need for further development.</t>
+          <t>Candidate Sania Gul possesses 16.0 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 11 recorded activity event(s), with 4 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Candidate 40_ABDUR_REHMAN has 4 years of experience with early career progression. Their timeline shows 8 events with 4 overlaps, including 2 suspicious ones, and 2 gaps, one of which is unjustified. The candidate lacks strong evidence of skills and has low job description alignment.</t>
+          <t>Candidate Abdur Rehman possesses 4.0 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 8 recorded activity event(s), with 4 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Candidate 42_SAQIB_JAMIL has 13.5 years of experience with a stable career progression. However, the presence of 3 suspicious overlaps and 2 unjustified gaps in their timeline raises concerns. Additionally, the candidate lacks strong evidence of relevant skills and has low job description alignment.</t>
+          <t>Candidate Saqib Jamil possesses 13.5 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 6 recorded activity event(s), with 3 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Candidate 43_AMMARA_NASIM has 13.8 years of experience with upward career progression. However, there are concerns with 5 overlaps, 2 gaps, and low JD alignment score, indicating potential inconsistencies in their professional history. Further clarification is needed to fully assess their qualifications.</t>
+          <t>Candidate Ammara Nasim possesses 13.8 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 5 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3336,9 +3336,13 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>IoT</t>
+        </is>
+      </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
@@ -3357,7 +3361,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Saqib possesses 0.0 years of total professional experience demonstrating a no professional experience listed trajectory. Their unified timeline contains 5 recorded activity event(s), with 0 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as No Experience Listed.</t>
+          <t>Candidate Muhammad Saqib possesses 0.0 years of total professional experience demonstrating a no professional experience listed trajectory. Their unified timeline contains 5 recorded activity event(s), with 0 overlap(s) and 2 gap(s) identified. Proven technical competencies include IoT, achieving a 0.0% position alignment score. Overall professional experience profile is classified as No Experience Listed.</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
@@ -26419,7 +26423,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -26428,7 +26432,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 2 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 4 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -26583,7 +26587,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -26592,7 +26596,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 12 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 9 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27198,7 +27202,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -27207,7 +27211,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 5 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 3 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27239,7 +27243,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -27248,7 +27252,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 2 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 4 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27362,7 +27366,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -27371,7 +27375,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Validated by 1 employment role(s) AND 6 publication(s).</t>
+          <t>Validated by 1 employment role(s) AND 2 publication(s).</t>
         </is>
       </c>
     </row>
@@ -27403,7 +27407,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -27412,7 +27416,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 4 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 2 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27444,7 +27448,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -27453,7 +27457,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 2 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 8 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27526,7 +27530,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -27535,7 +27539,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 20 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 19 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27567,7 +27571,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -27576,7 +27580,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 4 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 10 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27772,7 +27776,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -27781,7 +27785,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 9 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 12 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27813,7 +27817,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -27822,7 +27826,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 7 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 5 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -27970,23 +27974,23 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Moderate Evidence</t>
+          <t>Strong Evidence</t>
         </is>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jobs: [] | Pubs: [High Performance Triboelectric Nanogenerator Based on Metal-...]</t>
+          <t>Jobs: [] | Pubs: [High Performance Triboelectric Nanogenerator Based on Metal-...; Primary Theme: Wireless Networks &amp; IoT]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Supported by 0 job role(s) or 1 publication(s).</t>
+          <t>Demonstrated across multiple records (0 job(s), 2 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -28059,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -28068,7 +28072,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 5 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 4 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -28100,7 +28104,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -28109,7 +28113,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 6 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 5 paper(s)).</t>
         </is>
       </c>
     </row>
@@ -28141,7 +28145,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -28150,7 +28154,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Demonstrated across multiple records (0 job(s), 6 paper(s)).</t>
+          <t>Demonstrated across multiple records (0 job(s), 10 paper(s)).</t>
         </is>
       </c>
     </row>

--- a/data/analysis/experience_profiles.xlsx
+++ b/data/analysis/experience_profiles.xlsx
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Candidate Qamar Abbas possesses 8.0 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 3 recorded activity event(s), with 0 overlap(s) and 0 gap(s) identified. Proven technical competencies include IoT, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Strong Profile.</t>
+          <t>Candidate Qamar Abbas possesses 8.1 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 3 recorded activity event(s), with 0 overlap(s) and 0 gap(s) identified. Proven technical competencies include IoT, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Strong Profile.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Candidate MUHAMMAD MAJID possesses 4.9 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 7 recorded activity event(s), with 1 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
+          <t>Candidate MUHAMMAD MAJID possesses 5.0 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 7 recorded activity event(s), with 1 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Candidate Tayyaba Gull possesses 7.9 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
+          <t>Candidate Tayyaba Gull possesses 8.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Candidate M. Usman Abbasi possesses 16.7 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 7 recorded activity event(s), with 5 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
+          <t>Candidate M. Usman Abbasi possesses 16.8 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 7 recorded activity event(s), with 5 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Candidate Muzzamil Ghaffar possesses 14.3 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 4 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
+          <t>Candidate Muzzamil Ghaffar possesses 14.4 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 4 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Candidate Syed Fasih Ali possesses 2.4 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 7 recorded activity event(s), with 2 overlap(s) and 3 gap(s) identified. Proven technical competencies include IoT, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
+          <t>Candidate Syed Fasih Ali possesses 2.5 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 7 recorded activity event(s), with 2 overlap(s) and 3 gap(s) identified. Proven technical competencies include IoT, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Candidate Samana Batool possesses 8.4 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 4 recorded activity event(s), with 1 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
+          <t>Candidate Samana Batool possesses 8.6 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 4 recorded activity event(s), with 1 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Solid Profile.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Candidate MUHAMMAD SALMAN possesses 19.0 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 1 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate MUHAMMAD SALMAN possesses 19.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 1 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Candidate Nasir Ali Shah possesses 2.9 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 10 recorded activity event(s), with 7 overlap(s) and 4 gap(s) identified. Proven technical competencies include IoT, Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Nasir Ali Shah possesses 3.0 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 10 recorded activity event(s), with 7 overlap(s) and 4 gap(s) identified. Proven technical competencies include IoT, Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Candidate Farman Ali possesses 11.9 years of total professional experience demonstrating a steady career path trajectory. Their unified timeline contains 9 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Farman Ali possesses 12.0 years of total professional experience demonstrating a steady career path trajectory. Their unified timeline contains 9 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Candidate Fiza Murtaza possesses 13.8 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 14 recorded activity event(s), with 12 overlap(s) and 1 gap(s) identified. Proven technical competencies include Computer Vision, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Fiza Murtaza possesses 14.0 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 14 recorded activity event(s), with 12 overlap(s) and 1 gap(s) identified. Proven technical competencies include Computer Vision, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Abubakar possesses 9.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include Deep Learning, Machine Learning, achieving a 22.7% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Muhammad Abubakar possesses 9.2 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include Deep Learning, Machine Learning, achieving a 22.7% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Ehatisham possesses 9.9 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 11 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Muhammad Ehatisham possesses 10.0 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 11 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Candidate Waqas Amin possesses 14.0 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 3 gap(s) identified. Proven technical competencies include Cybersecurity, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Waqas Amin possesses 14.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 3 gap(s) identified. Proven technical competencies include Cybersecurity, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Candidate SYED TAMOORULHASSAN possesses 15.2 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 10 recorded activity event(s), with 4 overlap(s) and 2 gap(s) identified. Proven technical competencies include Wireless Networks, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate SYED TAMOORULHASSAN possesses 15.3 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 10 recorded activity event(s), with 4 overlap(s) and 2 gap(s) identified. Proven technical competencies include Wireless Networks, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1932,7 +1932,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Candidate Manzoor Ellahi possesses 17.8 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include IoT, Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Manzoor Ellahi possesses 17.9 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 6 overlap(s) and 2 gap(s) identified. Proven technical competencies include IoT, Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Candidate Sarosh Tahir possesses 17.3 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 12 recorded activity event(s), with 6 overlap(s) and 1 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Sarosh Tahir possesses 17.4 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 12 recorded activity event(s), with 6 overlap(s) and 1 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Candidate Suhail Asghar Qureshi possesses 0.8 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 6 recorded activity event(s), with 2 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Suhail Asghar Qureshi possesses 0.9 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 6 recorded activity event(s), with 2 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Candidate Muhammad Amjad possesses 8.9 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 11 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Muhammad Amjad possesses 9.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 11 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Candidate Asim Masood possesses 12.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Asim Masood possesses 12.2 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include Machine Learning, achieving a 9.1% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Candidate Saman Fatima possesses 5.1 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Saman Fatima possesses 5.2 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 3 overlap(s) and 4 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Candidate Zeeshan possesses 1.5 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 6 recorded activity event(s), with 2 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Zeeshan possesses 1.6 years of total professional experience demonstrating a early career trajectory. Their unified timeline contains 6 recorded activity event(s), with 2 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Candidate Waqas Tariq Toor possesses 17.4 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 5 overlap(s) and 3 gap(s) identified. Proven technical competencies include Artificial Intelligence, Deep Learning, IoT, achieving a 27.3% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Waqas Tariq Toor possesses 17.5 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 10 recorded activity event(s), with 5 overlap(s) and 3 gap(s) identified. Proven technical competencies include Artificial Intelligence, Deep Learning, IoT, achieving a 27.3% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Candidate Ahmed Naeem possesses 6.5 years of total professional experience demonstrating a steady career path trajectory. Their unified timeline contains 6 recorded activity event(s), with 3 overlap(s) and 0 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Ahmed Naeem possesses 6.6 years of total professional experience demonstrating a steady career path trajectory. Their unified timeline contains 6 recorded activity event(s), with 3 overlap(s) and 0 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Candidate Shaheer possesses 22.0 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 8 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Shaheer possesses 22.2 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 12 recorded activity event(s), with 8 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Candidate Fahd Sikandar Khan possesses 9.7 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 12 recorded activity event(s), with 5 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Fahd Sikandar Khan possesses 9.8 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 12 recorded activity event(s), with 5 overlap(s) and 3 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Candidate Shahzad possesses 9.3 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 4 overlap(s) and 1 gap(s) identified. Proven technical competencies include IoT, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Shahzad possesses 9.4 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 4 overlap(s) and 1 gap(s) identified. Proven technical competencies include IoT, achieving a 4.5% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Candidate Saqib Jamil possesses 13.5 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 6 recorded activity event(s), with 3 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Saqib Jamil possesses 13.6 years of total professional experience demonstrating a stable rank trajectory. Their unified timeline contains 6 recorded activity event(s), with 3 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Candidate Ammara Nasim possesses 13.8 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 5 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
+          <t>Candidate Ammara Nasim possesses 13.9 years of total professional experience demonstrating a upward progression trajectory. Their unified timeline contains 9 recorded activity event(s), with 5 overlap(s) and 2 gap(s) identified. Proven technical competencies include general domain competencies, achieving a 0.0% position alignment score. Overall professional experience profile is classified as Developing Profile.</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G147" t="b">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G251" t="b">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G252" t="b">
@@ -15664,7 +15664,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G351" t="b">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G353" t="b">
@@ -16380,11 +16380,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -17300,11 +17300,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -17420,11 +17420,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -17780,11 +17780,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -18420,11 +18420,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -19540,11 +19540,11 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -20860,11 +20860,11 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -21540,11 +21540,11 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -22180,11 +22180,11 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
